--- a/PrakashCRM/temp/MarketUpdate.xlsx
+++ b/PrakashCRM/temp/MarketUpdate.xlsx
@@ -88,7 +88,10 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>Add Test 123456789</x:t>
+    <x:t>11-02-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Add Test 123</x:t>
   </x:si>
   <x:si>
     <x:t>8</x:t>
@@ -121,250 +124,154 @@
     <x:t>abc</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29-08-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wejrkklwert</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tested</x:t>
-  </x:si>
-  <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>11-02-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>update</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-08-2025</x:t>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15-10-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Change in Rate of Benzaldehyde from Rs. 20 to Rs. 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E0028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arvind khatod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13-11-2025</x:t>
   </x:si>
   <x:si>
     <x:t>ok</x:t>
   </x:si>
   <x:si>
-    <x:t>E0028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arvind khatod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ok9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>qweweqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdfaf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>prsdumsn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdfsdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Praduman</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rej</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdfdsf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ewrwer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fdfdff</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testing Prashant</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test 17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wqeqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rytry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dssfsdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wereqwr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>546</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10393</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>erwer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rytrt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24-09-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>today test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E0044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FName01 LName01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>werfewr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ewfasdfsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54</x:t>
+    <x:t>Arvind k. khatod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-12-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Testing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E0013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAYUR PRAKASHBHAI SANT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-12-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abc test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29-12-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acetic Acid Price as on 29-12-2025 - 1200.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E0052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Diya Patel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31-12-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Price Has been updated By GNFC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05-02-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Testing RG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mr. Raj Guarv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-02-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tested by RG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-11-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11-02-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tester</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testers </x:t>
+  </x:si>
+  <x:si>
+    <x:t>73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>qweqweeqe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-04-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test adding market update 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E0029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rikesh Panchal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -428,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E50" totalsRowShown="0">
-  <x:autoFilter ref="A1:E50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E29" totalsRowShown="0">
+  <x:autoFilter ref="A1:E29"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Entry_No"/>
     <x:tableColumn id="2" name="Update_Date"/>
@@ -729,7 +636,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E50"/>
+  <x:dimension ref="A1:E29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:5">
@@ -856,10 +763,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>13</x:v>
@@ -870,13 +777,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>13</x:v>
@@ -887,13 +794,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>8</x:v>
@@ -904,13 +811,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>13</x:v>
@@ -921,13 +828,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>13</x:v>
@@ -938,13 +845,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>13</x:v>
@@ -955,13 +862,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>13</x:v>
@@ -972,614 +879,257 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="D15" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="D17" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:5">
-      <x:c r="A30" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:5">
-      <x:c r="A31" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:5">
-      <x:c r="A32" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:5">
-      <x:c r="A33" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:5">
-      <x:c r="A34" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:5">
-      <x:c r="A35" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:5">
-      <x:c r="A36" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:5">
-      <x:c r="A37" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:5">
-      <x:c r="A38" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:5">
-      <x:c r="A39" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:5">
-      <x:c r="A40" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:5">
-      <x:c r="A41" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:5">
-      <x:c r="A42" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:5">
-      <x:c r="A43" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:5">
-      <x:c r="A44" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:5">
-      <x:c r="A45" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:5">
-      <x:c r="A46" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:5">
-      <x:c r="A47" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:5">
-      <x:c r="A48" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:5">
-      <x:c r="A49" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:5">
-      <x:c r="A50" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
